--- a/inputData/inputDataBig.xlsx
+++ b/inputData/inputDataBig.xlsx
@@ -5,19 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FF8462-E867-F941-A476-B2EBA70288FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807D108D-5F36-D74B-B4D3-A6C8B4B741D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameters" sheetId="9" r:id="rId1"/>
-    <sheet name="Prices" sheetId="12" r:id="rId2"/>
-    <sheet name="PlaneData" sheetId="7" r:id="rId3"/>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId4"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId5"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>type</t>
   </si>
@@ -109,164 +107,16 @@
   </si>
   <si>
     <t>Base Vertiport</t>
-  </si>
-  <si>
-    <t>cap_u</t>
-  </si>
-  <si>
-    <t>bmax</t>
-  </si>
-  <si>
-    <t>bmin</t>
-  </si>
-  <si>
-    <t>ec</t>
-  </si>
-  <si>
-    <t>te</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>ET</t>
-  </si>
-  <si>
-    <t>fd_{i,j} = $3/km</t>
-  </si>
-  <si>
-    <t>fs_{i,j}=75% of fd_{i,j}</t>
-  </si>
-  <si>
-    <t>c_{i,j} = $1/km</t>
-  </si>
-  <si>
-    <t>e_{i,j} = 1%/km</t>
-  </si>
-  <si>
-    <t>seat capacity of eVTOL</t>
-  </si>
-  <si>
-    <t>minimum turnaround time at vertiport</t>
-  </si>
-  <si>
-    <t>maximum waiting time</t>
-  </si>
-  <si>
-    <t>end time</t>
-  </si>
-  <si>
-    <t>fare_stopover_factor</t>
-  </si>
-  <si>
-    <t>p_penalty</t>
-  </si>
-  <si>
-    <t>operating_cost_per_km</t>
-  </si>
-  <si>
-    <t>battery_per_km</t>
-  </si>
-  <si>
-    <t>time_per_km</t>
-  </si>
-  <si>
-    <t>fare_direct_per_km</t>
-  </si>
-  <si>
-    <t>Parameters</t>
-  </si>
-  <si>
-    <t>Bil tid (min)</t>
-  </si>
-  <si>
-    <t>Km fugleflugt</t>
-  </si>
-  <si>
-    <t>eVTOL flyvetid (min)</t>
-  </si>
-  <si>
-    <t>Hvor meget hurtigere</t>
-  </si>
-  <si>
-    <t>Fd km</t>
-  </si>
-  <si>
-    <t>Fd tid</t>
-  </si>
-  <si>
-    <t>fd max</t>
-  </si>
-  <si>
-    <t>Passager km pris</t>
-  </si>
-  <si>
-    <t>kr/km</t>
-  </si>
-  <si>
-    <t>Tidsværdi</t>
-  </si>
-  <si>
-    <t>kr/min</t>
-  </si>
-  <si>
-    <t>Lambda</t>
-  </si>
-  <si>
-    <t>Base fee</t>
-  </si>
-  <si>
-    <t>kr</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>fd_sum</t>
-  </si>
-  <si>
-    <t>2,1% battery charged per unit time</t>
-  </si>
-  <si>
-    <t>rt_{i,j} = 0.2 min/km</t>
-  </si>
-  <si>
-    <t>unit time</t>
-  </si>
-  <si>
-    <t>b_penalty</t>
-  </si>
-  <si>
-    <t>penalty for not serving passengergroup</t>
-  </si>
-  <si>
-    <t>penalty for exceeding bmax</t>
-  </si>
-  <si>
-    <t>bmid</t>
-  </si>
-  <si>
-    <t>opening_cost</t>
-  </si>
-  <si>
-    <t>cost of opening a vertiport</t>
-  </si>
-  <si>
-    <t>minuts/unit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -298,20 +148,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -334,34 +170,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -696,823 +512,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="5">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="5">
-        <v>400</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="5">
-        <v>300</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="5">
-        <v>1.51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="5">
-        <f>0.2/B20</f>
-        <v>0.04</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="5">
-        <v>100</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="5">
-        <v>80</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="5">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="5">
-        <v>20</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="5">
-        <f>2.11*B20</f>
-        <v>10.549999999999999</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="5">
-        <f>30/B20</f>
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="5">
-        <f>20/B20</f>
-        <v>4</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="5">
-        <f>120/B20</f>
-        <v>24</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="5">
-        <v>5</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10">
-        <v>2</v>
-      </c>
-      <c r="C2" s="10">
-        <f>(180)</f>
-        <v>180</v>
-      </c>
-      <c r="D2" s="10">
-        <v>219</v>
-      </c>
-      <c r="E2" s="10">
-        <f t="shared" ref="E2:E11" si="0">$M$1*D2</f>
-        <v>43.800000000000004</v>
-      </c>
-      <c r="F2" s="11">
-        <f>C2/E2</f>
-        <v>4.10958904109589</v>
-      </c>
-      <c r="G2" s="12">
-        <f t="shared" ref="G2:G11" si="1">D2*$M$2</f>
-        <v>4161</v>
-      </c>
-      <c r="H2" s="13">
-        <f t="shared" ref="H2:H11" si="2">(C2-E2)*$M$3*$M$4</f>
-        <v>1589</v>
-      </c>
-      <c r="I2" s="13">
-        <f>G2+H2</f>
-        <v>5750</v>
-      </c>
-      <c r="J2" s="13">
-        <f t="shared" ref="J2:J11" si="3">MAX($M$2*D2+$M$5,$M$4*$M$3*(C2-E2))</f>
-        <v>4161</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" s="5">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10">
-        <v>60</v>
-      </c>
-      <c r="D3" s="10">
-        <v>88</v>
-      </c>
-      <c r="E3" s="10">
-        <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
-      </c>
-      <c r="F3" s="11">
-        <f t="shared" ref="F3:F11" si="4">C3/E3</f>
-        <v>3.4090909090909087</v>
-      </c>
-      <c r="G3" s="12">
-        <f t="shared" si="1"/>
-        <v>1672</v>
-      </c>
-      <c r="H3" s="13">
-        <f t="shared" si="2"/>
-        <v>494.66666666666669</v>
-      </c>
-      <c r="I3" s="13">
-        <f t="shared" ref="I3:I11" si="5">G3+H3</f>
-        <v>2166.6666666666665</v>
-      </c>
-      <c r="J3" s="13">
-        <f t="shared" si="3"/>
-        <v>1672</v>
-      </c>
-      <c r="L3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="5">
-        <f>1000/60</f>
-        <v>16.666666666666668</v>
-      </c>
-      <c r="N3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10">
-        <v>4</v>
-      </c>
-      <c r="C4" s="10">
-        <f>200</f>
-        <v>200</v>
-      </c>
-      <c r="D4" s="10">
-        <v>147</v>
-      </c>
-      <c r="E4" s="10">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
-      </c>
-      <c r="F4" s="11">
-        <f t="shared" si="4"/>
-        <v>6.8027210884353737</v>
-      </c>
-      <c r="G4" s="12">
-        <f t="shared" si="1"/>
-        <v>2793</v>
-      </c>
-      <c r="H4" s="13">
-        <f t="shared" si="2"/>
-        <v>1990.3333333333333</v>
-      </c>
-      <c r="I4" s="13">
-        <f t="shared" si="5"/>
-        <v>4783.333333333333</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" si="3"/>
-        <v>2793</v>
-      </c>
-      <c r="L4" t="s">
-        <v>56</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="10">
-        <v>5</v>
-      </c>
-      <c r="C5" s="10">
-        <f>(60+50)</f>
-        <v>110</v>
-      </c>
-      <c r="D5" s="10">
-        <v>147</v>
-      </c>
-      <c r="E5" s="10">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
-      </c>
-      <c r="F5" s="11">
-        <f t="shared" si="4"/>
-        <v>3.7414965986394555</v>
-      </c>
-      <c r="G5" s="12">
-        <f t="shared" si="1"/>
-        <v>2793</v>
-      </c>
-      <c r="H5" s="13">
-        <f t="shared" si="2"/>
-        <v>940.33333333333326</v>
-      </c>
-      <c r="I5" s="13">
-        <f t="shared" si="5"/>
-        <v>3733.333333333333</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="3"/>
-        <v>2793</v>
-      </c>
-      <c r="L5" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10">
-        <f>(120+40)</f>
-        <v>160</v>
-      </c>
-      <c r="D6" s="10">
-        <v>131</v>
-      </c>
-      <c r="E6" s="10">
-        <f t="shared" si="0"/>
-        <v>26.200000000000003</v>
-      </c>
-      <c r="F6" s="11">
-        <f t="shared" si="4"/>
-        <v>6.1068702290076331</v>
-      </c>
-      <c r="G6" s="12">
-        <f t="shared" si="1"/>
-        <v>2489</v>
-      </c>
-      <c r="H6" s="13">
-        <f t="shared" si="2"/>
-        <v>1561.0000000000002</v>
-      </c>
-      <c r="I6" s="13">
-        <f t="shared" si="5"/>
-        <v>4050</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="3"/>
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10">
-        <f>90</f>
-        <v>90</v>
-      </c>
-      <c r="D7" s="10">
-        <v>111</v>
-      </c>
-      <c r="E7" s="10">
-        <f t="shared" si="0"/>
-        <v>22.200000000000003</v>
-      </c>
-      <c r="F7" s="11">
-        <f t="shared" si="4"/>
-        <v>4.0540540540540535</v>
-      </c>
-      <c r="G7" s="12">
-        <f t="shared" si="1"/>
-        <v>2109</v>
-      </c>
-      <c r="H7" s="13">
-        <f t="shared" si="2"/>
-        <v>791</v>
-      </c>
-      <c r="I7" s="13">
-        <f t="shared" si="5"/>
-        <v>2900</v>
-      </c>
-      <c r="J7" s="13">
-        <f t="shared" si="3"/>
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="10">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10">
-        <f>75</f>
-        <v>75</v>
-      </c>
-      <c r="D8" s="10">
-        <v>80</v>
-      </c>
-      <c r="E8" s="10">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F8" s="11">
-        <f t="shared" si="4"/>
-        <v>4.6875</v>
-      </c>
-      <c r="G8" s="12">
-        <f t="shared" si="1"/>
-        <v>1520</v>
-      </c>
-      <c r="H8" s="13">
-        <f t="shared" si="2"/>
-        <v>688.33333333333337</v>
-      </c>
-      <c r="I8" s="13">
-        <f t="shared" si="5"/>
-        <v>2208.3333333333335</v>
-      </c>
-      <c r="J8" s="13">
-        <f t="shared" si="3"/>
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" s="10">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10">
-        <v>180</v>
-      </c>
-      <c r="D9" s="10">
-        <v>79</v>
-      </c>
-      <c r="E9" s="10">
-        <f t="shared" si="0"/>
-        <v>15.8</v>
-      </c>
-      <c r="F9" s="11">
-        <f t="shared" si="4"/>
-        <v>11.39240506329114</v>
-      </c>
-      <c r="G9" s="12">
-        <f t="shared" si="1"/>
-        <v>1501</v>
-      </c>
-      <c r="H9" s="13">
-        <f t="shared" si="2"/>
-        <v>1915.6666666666665</v>
-      </c>
-      <c r="I9" s="13">
-        <f t="shared" si="5"/>
-        <v>3416.6666666666665</v>
-      </c>
-      <c r="J9" s="13">
-        <f t="shared" si="3"/>
-        <v>1915.6666666666665</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" s="10">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10">
-        <v>90</v>
-      </c>
-      <c r="D10" s="10">
-        <v>63</v>
-      </c>
-      <c r="E10" s="10">
-        <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
-      </c>
-      <c r="F10" s="11">
-        <f t="shared" si="4"/>
-        <v>7.1428571428571423</v>
-      </c>
-      <c r="G10" s="12">
-        <f t="shared" si="1"/>
-        <v>1197</v>
-      </c>
-      <c r="H10" s="13">
-        <f t="shared" si="2"/>
-        <v>903.00000000000011</v>
-      </c>
-      <c r="I10" s="13">
-        <f t="shared" si="5"/>
-        <v>2100</v>
-      </c>
-      <c r="J10" s="13">
-        <f t="shared" si="3"/>
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" s="10">
-        <v>5</v>
-      </c>
-      <c r="C11" s="10">
-        <v>120</v>
-      </c>
-      <c r="D11" s="10">
-        <v>93</v>
-      </c>
-      <c r="E11" s="10">
-        <f t="shared" si="0"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="F11" s="11">
-        <f t="shared" si="4"/>
-        <v>6.4516129032258061</v>
-      </c>
-      <c r="G11" s="12">
-        <f t="shared" si="1"/>
-        <v>1767</v>
-      </c>
-      <c r="H11" s="13">
-        <f t="shared" si="2"/>
-        <v>1183</v>
-      </c>
-      <c r="I11" s="13">
-        <f t="shared" si="5"/>
-        <v>2950</v>
-      </c>
-      <c r="J11" s="13">
-        <f t="shared" si="3"/>
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" s="10">
-        <v>1</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="12"/>
-      <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13" s="10">
-        <v>2</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14" s="10">
-        <v>3</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15" s="10">
-        <v>4</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16" s="10">
-        <v>5</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5">
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="5:5">
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="5:5">
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="5:5">
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="5:5">
-      <c r="E24" s="1"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="G2:G11">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -1565,7 +564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -1675,10 +674,10 @@
       </c>
     </row>
     <row r="18" spans="4:5">
-      <c r="E18" s="6"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="20" spans="4:5">
-      <c r="D20" s="6"/>
+      <c r="D20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1686,7 +685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>

--- a/inputData/inputDataBig.xlsx
+++ b/inputData/inputDataBig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807D108D-5F36-D74B-B4D3-A6C8B4B741D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37525185-01B2-4036-9C3B-3B2C2188F01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="7740" yWindow="0" windowWidth="11460" windowHeight="11280" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -100,13 +100,13 @@
     <t>stopover_allowed</t>
   </si>
   <si>
-    <t>coordinates_kbh</t>
-  </si>
-  <si>
     <t>Plane ID</t>
   </si>
   <si>
     <t>Base Vertiport</t>
+  </si>
+  <si>
+    <t>coordinates</t>
   </si>
 </sst>
 </file>
@@ -514,17 +514,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -567,7 +567,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -585,7 +585,7 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -688,7 +688,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>

--- a/inputData/inputDataBig.xlsx
+++ b/inputData/inputDataBig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807D108D-5F36-D74B-B4D3-A6C8B4B741D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F63FAC-751D-EC43-A995-567CFCB157E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -100,13 +100,13 @@
     <t>stopover_allowed</t>
   </si>
   <si>
-    <t>coordinates_kbh</t>
-  </si>
-  <si>
     <t>Plane ID</t>
   </si>
   <si>
     <t>Base Vertiport</t>
+  </si>
+  <si>
+    <t>coordinates</t>
   </si>
 </sst>
 </file>
@@ -521,10 +521,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -585,7 +585,7 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6">
